--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +463,21 @@
           <t>LinkedIn</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Date Added</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,6 +510,9 @@
           <t>https://linkedin.com/company/mikesplumbing</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,6 +545,9 @@
           <t>https://linkedin.com/company/desertairhvac</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -554,6 +579,173 @@
         <is>
           <t>https://linkedin.com/company/phxroofing</t>
         </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ethan Wells</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sunset Construction Services</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://sunsetconstructionservices.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>gregperger@gmail.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Google Maps (sample)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>46120.81544764517</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nina Alvarez</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pinnacle Builders</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://pinnaclebuildersaz.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>info@pinnaclebuildersaz.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Google Maps (sample)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>46120.81544764536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ari Becker</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ridge Line Builders</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://ridgelinebuilders.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dave@ridgelinebuilders.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2020-10-20</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Google Maps (sample)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>46120.81544764539</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ariel Gonzalez</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Phoenix Construction Co</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://phoenixconstructionco.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>info@phoenixconstructionco.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>46120.81544764539</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46120.81544764517</v>
+        <v>46120.81544765046</v>
       </c>
     </row>
     <row r="6">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46120.81544764536</v>
+        <v>46120.81544765046</v>
       </c>
     </row>
     <row r="7">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46120.81544764539</v>
+        <v>46120.81544765046</v>
       </c>
     </row>
     <row r="8">
@@ -745,7 +745,1866 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46120.81544764539</v>
+        <v>46120.81544765046</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Carlos Ramirez</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Miami Home Renovations</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://mihomesreno.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>info@mihomesreno.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Google Maps (sample)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>46120.82280933936</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sofia Lopez</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Palm Beach Contractors</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://palmbeachcontractors.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>info@palmbeachcontractors.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Google Maps (sample)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>46120.82280933944</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Contact 4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Valley Concrete</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://valleyconcrete.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>user@domain.com.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1618513208426</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>46120.82280933946</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Contact 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale Builders</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://fortlauderdalebuilders.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>46120.82280933949</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Contact 8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>South Florida Excavation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://southfloridaexcavation.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>info@southfloridaexcavation.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>46120.8228093395</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Contact 9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Coastal Construction Co</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://coastalconstructionco.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>fancybox@3.5.7</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>46120.82280933952</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Contact 10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tropical Builders</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://tropicalbuilders.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>46120.82280933954</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Contact 11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Everglades Contractors</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://evergladescontractors.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>info@evergladescontractors.com</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>46120.82280933955</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Contact 12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Beachside Renovations</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://beachsiderenovations.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>63101157</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>46120.82280933956</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Contact 13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Key West Construction</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://keywestconstruction.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>user@domain.com.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4211612264</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>46120.82280933958</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Contact 14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Coral Gables Builders</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://coralgablesbuilders.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>info@coralgablesbuilders.com</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>46120.8228093396</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Contact 15</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brickell Contractors</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://brickellcontractors.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>info@brickellcontractors.com</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>46120.82280933961</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Contact 16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Wynwood Renovations</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://wynwoodrenovations.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>info@wynwoodrenovations.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>46120.82280933962</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Contact 17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Little Havana Builders</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://littlehavanabuilders.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>info@littlehavanabuilders.com</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>46120.82280933963</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Contact 18</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Doral Construction</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://doralconstruction.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>info@doralconstruction.com</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>46120.82280933964</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Contact 19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kendall Contractors</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://kendallcontractors.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>info@kendallcontractors.com</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>46120.82280933965</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Contact 20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Homestead Builders</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://homesteadbuilders.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>46120.82280933966</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Contact 21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cutler Bay Renovations</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://cutlerbayrenovations.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>info@cutlerbayrenovations.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>46120.82280933968</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Contact 22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pinecrest Construction</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://pinecrestconstruction.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>info@pinecrestconstruction.com</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>46120.82280933969</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Contact 23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>South Miami Builders</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://southmiamibuilders.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>+0152-0153</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>46120.8228093397</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Contact 24</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gables Contractors</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://gablescontractors.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>info@gablescontractors.com</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>46120.82280933972</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Contact 25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bal Harbour Renovations</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://balharbourrenovations.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>info@balharbourrenovations.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>46120.82280933973</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Contact 26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Surfside Builders</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://surfsidebuilders.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>46120.82280933975</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Contact 27</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sunny Isles Construction</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://sunnyislesconstruction.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>info@sunnyislesconstruction.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>46120.82280933976</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Contact 28</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Aventura Contractors</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://aventuracontractors.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>info@aventuracontractors.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>46120.82280933977</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Contact 29</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Hallandale Builders</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://hallandalebuilders.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>info@hallandalebuilders.com</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>46120.82280933978</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Contact 30</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hollywood Renovations</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://hollywoodrenovations.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>info@hollywoodrenovations.com</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>46120.82280933979</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Contact 31</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pembroke Pines Construction</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://pembrokepinesconstruction.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>info@pembrokepinesconstruction.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>46120.82280933981</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Contact 32</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Miramar Contractors</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://miramarcontractors.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>info@miramarcontractors.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>46120.82280933981</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Contact 33</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Davie Builders</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://daviebuilders.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>+0400-045</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>46120.82280933983</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Contact 34</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Cooper City Renovations</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://coopercityrenovations.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>info@coopercityrenovations.com</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>46120.82280933984</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Contact 35</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Weston Construction</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://westonconstruction.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>info@westonconstruction.com</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>46120.82280933985</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Contact 36</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Plantation Contractors</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://plantationcontractors.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>info@plantationcontractors.com</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>46120.82280933987</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Contact 37</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sunrise Builders</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://sunrisebuilders.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>info@sunrisebuilders.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>46120.82280933987</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Contact 38</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Lauderhill Renovations</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://lauderhillrenovations.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>info@lauderhillrenovations.com</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>46120.82280933989</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Contact 39</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tamarac Construction</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://tamaracconstruction.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>info@tamaracconstruction.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>46120.82280933989</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Contact 40</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Coral Springs Contractors</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://coralspringscontractors.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>info@coralspringscontractors.com</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>46120.82280933991</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Contact 41</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Parkland Builders</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://parklandbuilders.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>46120.82280933992</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Contact 42</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Margate Renovations</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://margaterenovations.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>info@margaterenovations.com</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>46120.82280933993</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Contact 43</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Coconut Creek Construction</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://coconutcreekconstruction.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>info@coconutcreekconstruction.com</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>46120.82280933994</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Contact 44</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deerfield Beach Contractors</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://deerfieldbeachcontractors.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>info@deerfieldbeachcontractors.com</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>46120.82280933995</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Contact 45</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Boca Raton Builders</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://bocaratonbuilders.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>46120.82280934009</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Contact 46</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Delray Beach Renovations</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://delraybeachrenovations.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>46120.8228093401</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Contact 47</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Boynton Beach Construction</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://boyntonbeachconstruction.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>info@boyntonbeachconstruction.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>46120.82280934011</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Contact 48</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Lake Worth Contractors</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://lakeworthcontractors.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>info@lakeworthcontractors.com</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>46120.82280934013</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Contact 49</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>West Palm Beach Builders</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://westpalmbeachbuilders.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>info@westpalmbeachbuilders.com</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>46120.82280934014</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Contact 50</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens Renovations</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://palmbeachgardensrenovations.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>info@palmbeachgardensrenovations.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Thumbtack (sample)</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>46120.82280934015</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46120.82280933936</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="10">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46120.82280933944</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="11">
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46120.82280933946</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="12">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46120.82280933949</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="13">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46120.8228093395</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="14">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46120.82280933952</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="15">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46120.82280933954</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="16">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46120.82280933955</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="17">
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46120.82280933956</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="18">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46120.82280933958</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="19">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46120.8228093396</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="20">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46120.82280933961</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="21">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46120.82280933962</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="22">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46120.82280933963</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="23">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46120.82280933964</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="24">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46120.82280933965</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="25">
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46120.82280933966</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="26">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46120.82280933968</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="27">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46120.82280933969</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="28">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46120.8228093397</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="29">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46120.82280933972</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="30">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46120.82280933973</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="31">
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46120.82280933975</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="32">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46120.82280933976</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="33">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46120.82280933977</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="34">
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46120.82280933978</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="35">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46120.82280933979</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="36">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46120.82280933981</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="37">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46120.82280933981</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="38">
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46120.82280933983</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="39">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46120.82280933984</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="40">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46120.82280933985</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="41">
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46120.82280933987</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="42">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46120.82280933987</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="43">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46120.82280933989</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="44">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46120.82280933989</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="45">
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46120.82280933991</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="46">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46120.82280933992</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="47">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46120.82280933993</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="48">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46120.82280933994</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="49">
@@ -2374,7 +2374,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46120.82280933995</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="50">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46120.82280934009</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="51">
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46120.8228093401</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="52">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46120.82280934011</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="53">
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46120.82280934013</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="54">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46120.82280934014</v>
+        <v>46120.82280934028</v>
       </c>
     </row>
     <row r="55">
@@ -2604,7 +2604,1442 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46120.82280934015</v>
+        <v>46120.82280934028</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Contact 1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Everglades Construction</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/everglades-construction</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/everglades-construction</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>46120.82763860016</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Contact 3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Brickell Renovations</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/brickell-renovations</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/brickell-renovations</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>46120.82763860027</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Contact 4</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Wynwood Contractors</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/wynwood-contractors</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/wynwood-contractors</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>46120.82763860029</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Contact 6</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Doral Renovations</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/doral-renovations</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/doral-renovations</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>46120.8276386003</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Contact 7</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kendall Construction</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/kendall-construction</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/kendall-construction</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>46120.82763860033</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Contact 9</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cutler Bay Contractors</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/cutler-bay-contractors</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/cutler-bay-contractors</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>46120.82763860033</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Contact 10</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pinecrest Renovations</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/pinecrest-renovations</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/pinecrest-renovations</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>46120.82763860035</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Contact 17</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hallandale Renovations</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/hallandale-renovations</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/hallandale-renovations</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>46120.82763860037</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Contact 18</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Hollywood Builders</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/hollywood-builders</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/hollywood-builders</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>46120.82763860039</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Contact 19</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pembroke Pines Contractors</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/pembroke-pines-contractors</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/pembroke-pines-contractors</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>46120.82763860039</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Contact 20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Miramar Renovations</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/miramar-renovations</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/miramar-renovations</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>46120.82763860041</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Contact 22</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Cooper City Construction</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/cooper-city-construction</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/cooper-city-construction</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>46120.82763860043</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Contact 23</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Weston Contractors</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/weston-contractors</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/weston-contractors</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>46120.82763860044</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Contact 24</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Plantation Builders</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/plantation-builders</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/plantation-builders</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>46120.82763860045</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Contact 25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sunrise Renovations</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/sunrise-renovations</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/sunrise-renovations</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>46120.82763860047</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Contact 26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lauderhill Construction</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/lauderhill-construction</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/lauderhill-construction</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>46120.82763860047</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Contact 27</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tamarac Contractors</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/tamarac-contractors</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/tamarac-contractors</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>46120.82763860049</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Contact 28</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Coral Springs Builders</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/coral-springs-builders</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/coral-springs-builders</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>46120.82763860049</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Contact 29</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Parkland Renovations</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/parkland-renovations</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/parkland-renovations</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>46120.82763860051</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Contact 30</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Margate Construction</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/margate-construction</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/margate-construction</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>46120.82763860053</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Contact 31</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Coconut Creek Contractors</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/coconut-creek-contractors</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/coconut-creek-contractors</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>46120.82763860055</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Contact 32</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deerfield Beach Builders</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/deerfield-beach-builders</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/deerfield-beach-builders</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>46120.82763860055</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Contact 33</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Boca Raton Renovations</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/boca-raton-renovations</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/boca-raton-renovations</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>46120.82763860057</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Contact 34</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Delray Beach Construction</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/delray-beach-construction</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/delray-beach-construction</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>46120.82763860058</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Contact 35</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Boynton Beach Contractors</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/boynton-beach-contractors</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/boynton-beach-contractors</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>46120.82763860058</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Contact 36</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Lake Worth Builders</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/lake-worth-builders</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/lake-worth-builders</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>46120.8276386006</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Contact 37</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>West Palm Beach Renovations</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/west-palm-beach-renovations</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/west-palm-beach-renovations</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>46120.82763860061</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Contact 38</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Palm Beach Gardens Construction</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/palm-beach-gardens-construction</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/palm-beach-gardens-construction</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>46120.82763860063</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Contact 39</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Jupiter Contractors</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/jupiter-contractors</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/jupiter-contractors</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>46120.82763860063</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Contact 40</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Stuart Builders</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/stuart-builders</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/stuart-builders</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>46120.82763860064</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Contact 41</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Port St. Lucie Renovations</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/port-st.-lucie-renovations</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/port-st.-lucie-renovations</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>46120.82763860065</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Contact 42</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Fort Pierce Construction</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/fort-pierce-construction</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/fort-pierce-construction</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>46120.82763860086</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Contact 43</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Stuart Contractors</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/stuart-contractors</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/stuart-contractors</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>46120.82763860087</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Contact 44</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Port St. Lucie Builders</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/port-st.-lucie-builders</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/port-st.-lucie-builders</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>46120.82763860089</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Contact 45</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Fort Pierce Renovations</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://yelp.com/biz/fort-pierce-renovations</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>info@yelp.com/biz/fort-pierce-renovations</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Yelp (sample)</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>46120.82763860089</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46120.82763860016</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="57">
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46120.82763860027</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="58">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46120.82763860029</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="59">
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46120.8276386003</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="60">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46120.82763860033</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="61">
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46120.82763860033</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="62">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46120.82763860035</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="63">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46120.82763860037</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="64">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46120.82763860039</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="65">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46120.82763860039</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="66">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46120.82763860041</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="67">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46120.82763860043</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="68">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46120.82763860044</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="69">
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46120.82763860045</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="70">
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46120.82763860047</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="71">
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46120.82763860047</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="72">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46120.82763860049</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="73">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46120.82763860049</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="74">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46120.82763860051</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="75">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46120.82763860053</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="76">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46120.82763860055</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="77">
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46120.82763860055</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="78">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46120.82763860057</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="79">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46120.82763860058</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="80">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46120.82763860058</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="81">
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46120.8276386006</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="82">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46120.82763860061</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="83">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46120.82763860063</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="84">
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46120.82763860063</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="85">
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46120.82763860064</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="86">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46120.82763860065</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="87">
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46120.82763860086</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="88">
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46120.82763860087</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="89">
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46120.82763860089</v>
+        <v>46120.82763859953</v>
       </c>
     </row>
     <row r="90">
@@ -4039,7 +4039,2016 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46120.82763860089</v>
+        <v>46120.82763859953</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Contact 1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Bayfront Builders</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/bayfront-builders</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/bayfront-builders</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>46120.83146243726</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Contact 2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Oceanview Contractors</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/oceanview-contractors</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/oceanview-contractors</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>46120.83146243736</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Contact 3</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Island Renovations</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/island-renovations</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/island-renovations</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>46120.83146243737</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Contact 5</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Harbor Builders</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/harbor-builders</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/harbor-builders</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>46120.8314624374</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Contact 6</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Marina Renovations</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/marina-renovations</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/marina-renovations</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>46120.83146243741</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Contact 7</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Lagoon Contractors</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/lagoon-contractors</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/lagoon-contractors</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>46120.83146243743</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Contact 8</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Key Builders</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/key-builders</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/key-builders</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>46120.83146243744</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Contact 9</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Shoreline Construction</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/shoreline-construction</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/shoreline-construction</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>46120.83146243745</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Contact 10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Reef Renovations</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/reef-renovations</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/reef-renovations</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>46120.83146243747</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Contact 11</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Cove Contractors</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/cove-contractors</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/cove-contractors</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>46120.83146243748</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Contact 12</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Inlet Builders</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/inlet-builders</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/inlet-builders</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>46120.83146243749</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Contact 13</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Sound Construction</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/sound-construction</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/sound-construction</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>46120.8314624375</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Contact 14</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Estuary Renovations</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/estuary-renovations</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/estuary-renovations</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>46120.83146243751</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Contact 15</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Fjord Contractors</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/fjord-contractors</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/fjord-contractors</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>46120.83146243752</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Contact 16</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Delta Builders</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/delta-builders</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/delta-builders</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>46120.83146243752</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Contact 17</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Gulf Construction</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/gulf-construction</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/gulf-construction</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>46120.83146243753</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Contact 18</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Bayou Renovations</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/bayou-renovations</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/bayou-renovations</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>46120.83146243755</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Contact 19</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Strait Contractors</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/strait-contractors</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/strait-contractors</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>46120.83146243756</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Contact 20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Channel Builders</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/channel-builders</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/channel-builders</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>46120.83146243756</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Contact 21</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Peninsula Construction</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/peninsula-construction</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/peninsula-construction</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>46120.83146243757</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Contact 22</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Isthmus Renovations</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/isthmus-renovations</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/isthmus-renovations</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>46120.83146243758</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Contact 23</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Cape Contractors</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/cape-contractors</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/cape-contractors</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>46120.83146243759</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Contact 24</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Point Builders</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/point-builders</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/point-builders</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>46120.83146243761</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Contact 25</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Headland Construction</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/headland-construction</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/headland-construction</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>46120.83146243761</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Contact 26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Neck Renovations</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/neck-renovations</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/neck-renovations</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>46120.83146243763</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Contact 27</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Spit Contractors</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/spit-contractors</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/spit-contractors</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>46120.83146243764</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Contact 28</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Tombolo Builders</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/tombolo-builders</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/tombolo-builders</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>46120.83146243765</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Contact 29</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Hook Construction</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/hook-construction</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/hook-construction</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>46120.83146243767</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Contact 30</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Bar Renovations</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/bar-renovations</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/bar-renovations</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>46120.83146243767</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Contact 31</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sandbar Contractors</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/sandbar-contractors</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/sandbar-contractors</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>46120.83146243767</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Contact 32</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Dune Builders</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/dune-builders</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/dune-builders</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>46120.83146243769</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Contact 33</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Beach Construction</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/beach-construction</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/beach-construction</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>46120.83146243783</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Contact 34</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Dune Renovations</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/dune-renovations</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/dune-renovations</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>46120.83146243783</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Contact 35</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Shore Contractors</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/shore-contractors</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/shore-contractors</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>46120.83146243786</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Contact 36</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Coast Builders</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/coast-builders</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/coast-builders</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>46120.83146243786</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Contact 37</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Seaside Construction</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/seaside-construction</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/seaside-construction</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>46120.83146243787</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Contact 38</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Littoral Renovations</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/littoral-renovations</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/littoral-renovations</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>46120.83146243788</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Contact 39</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Riparian Contractors</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/riparian-contractors</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/riparian-contractors</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>46120.83146243789</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Contact 40</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Fluvial Builders</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/fluvial-builders</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/fluvial-builders</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>46120.83146243791</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Contact 41</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Riverine Construction</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/riverine-construction</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/riverine-construction</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>46120.83146243792</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Contact 42</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Lacustrine Renovations</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/lacustrine-renovations</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/lacustrine-renovations</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>46120.83146243792</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Contact 43</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Palustrine Contractors</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/palustrine-contractors</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/palustrine-contractors</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>46120.83146243794</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Contact 44</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Bog Builders</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/bog-builders</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/bog-builders</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>46120.83146243795</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Contact 45</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Marsh Construction</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/marsh-construction</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/marsh-construction</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>46120.83146243796</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Contact 46</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Swamp Renovations</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/swamp-renovations</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/swamp-renovations</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>46120.83146243796</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Contact 47</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Fen Contractors</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/fen-contractors</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/fen-contractors</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>46120.83146243797</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Contact 48</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Moor Builders</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/moor-builders</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/moor-builders</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>46120.83146243799</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Contact 49</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Heath Construction</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/heath-construction</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/heath-construction</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>46120.831462438</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Contact 50</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Moorland Renovations</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://foursquare.com/v/moorland-renovations</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>info@foursquare.com/v/moorland-renovations</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>602-555-1234</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Foursquare (sample)</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>46120.831462438</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46120.83146243726</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="92">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46120.83146243736</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="93">
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46120.83146243737</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="94">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46120.8314624374</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="95">
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46120.83146243741</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="96">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46120.83146243743</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="97">
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46120.83146243744</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="98">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46120.83146243745</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="99">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46120.83146243747</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="100">
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46120.83146243748</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="101">
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46120.83146243749</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="102">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46120.8314624375</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="103">
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46120.83146243751</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="104">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46120.83146243752</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="105">
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46120.83146243752</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="106">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46120.83146243753</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="107">
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46120.83146243755</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="108">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46120.83146243756</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="109">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46120.83146243756</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="110">
@@ -4859,7 +4859,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46120.83146243757</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="111">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46120.83146243758</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="112">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46120.83146243759</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="113">
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46120.83146243761</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="114">
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46120.83146243761</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="115">
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46120.83146243763</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="116">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46120.83146243764</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="117">
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46120.83146243765</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="118">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46120.83146243767</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="119">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46120.83146243767</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="120">
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46120.83146243767</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="121">
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46120.83146243769</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="122">
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46120.83146243783</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="123">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46120.83146243783</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="124">
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46120.83146243786</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="125">
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46120.83146243786</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="126">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46120.83146243787</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="127">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46120.83146243788</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="128">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46120.83146243789</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="129">
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46120.83146243791</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="130">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46120.83146243792</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="131">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46120.83146243792</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="132">
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46120.83146243794</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="133">
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46120.83146243795</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="134">
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46120.83146243796</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="135">
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46120.83146243796</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="136">
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46120.83146243797</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="137">
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46120.83146243799</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="138">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46120.831462438</v>
+        <v>46120.83146244213</v>
       </c>
     </row>
     <row r="139">
@@ -6048,7 +6048,1861 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46120.831462438</v>
+        <v>46120.83146244213</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Contact 1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Evergreen Builders</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Evergreen+Builders</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>46120.83443639865</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Contact 2</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Summit Contractors</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Summit+Contractors</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>46120.83443639877</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Contact 3</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Vertex Construction</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Vertex+Construction</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>95572165</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>46120.8344363988</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Contact 4</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Apex Renovations</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Apex+Renovations</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>46120.83443639882</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Contact 5</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Zenith Builders</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Zenith+Builders</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>46120.83443639883</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Contact 6</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Nadir Contractors</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Nadir+Contractors</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>46120.83443639885</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Contact 7</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Pinnacle Construction</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Pinnacle+Construction</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>46120.83443639887</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Contact 8</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Base Renovations</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Base+Renovations</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>46120.83443639889</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Contact 9</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Crown Builders</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Crown+Builders</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>273515132</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>46120.8344363989</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Contact 10</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Foundation Contractors</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Foundation+Contractors</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>46120.83443639891</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Contact 11</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Roof Construction</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Roof+Construction</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>46120.83443639892</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Contact 12</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Wall Renovations</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Wall+Renovations</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>4043918790</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>46120.83443639894</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Contact 13</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Floor Builders</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Floor+Builders</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>5799606901511</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>46120.83443639895</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Contact 14</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Ceiling Contractors</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Ceiling+Contractors</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>46120.83443639896</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Contact 15</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Door Construction</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Door+Construction</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>sales@citydoor.com</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>46120.83443639898</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Contact 16</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Window Renovations</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Window+Renovations</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>46120.834436399</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Contact 17</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Frame Builders</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Frame+Builders</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>46120.834436399</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Contact 18</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Siding Contractors</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Siding+Contractors</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>46120.83443639903</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Contact 19</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Insulation Construction</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Insulation+Construction</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>46120.83443639903</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Contact 20</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Drywall Renovations</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Drywall+Renovations</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>46120.83443639906</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Contact 21</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Paint Builders</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Paint+Builders</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>11787541</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>46120.83443639908</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Contact 22</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Tile Contractors</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Tile+Contractors</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>46120.83443639908</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Contact 23</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Carpet Construction</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Carpet+Construction</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>46120.83443639908</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Contact 24</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Hardwood Renovations</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Hardwood+Renovations</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>46120.8344363991</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Contact 25</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Laminate Builders</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Laminate+Builders</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>46120.83443639911</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Contact 26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Vinyl Contractors</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Vinyl+Contractors</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>53299563</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>46120.83443639913</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Contact 27</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Stone Construction</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Stone+Construction</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>46120.83443639914</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Contact 28</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Brick Renovations</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Brick+Renovations</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>46120.83443639916</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Contact 29</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Concrete Builders</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Concrete+Builders</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>46120.83443639932</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Contact 30</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Asphalt Contractors</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Asphalt+Contractors</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>46120.83443639933</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Contact 31</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Gravel Construction</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Gravel+Construction</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>96234612</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>46120.83443639934</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Contact 32</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Sand Renovations</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Sand+Renovations</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>46120.83443639935</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Contact 33</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Dirt Builders</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Dirt+Builders</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>84045539</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>46120.83443639936</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Contact 34</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Mud Contractors</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Mud+Contractors</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>46120.83443639937</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Contact 35</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Clay Construction</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Clay+Construction</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>46120.83443639939</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Contact 36</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Loam Renovations</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Loam+Renovations</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>46120.8344363994</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Contact 37</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Silt Builders</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Silt+Builders</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>46120.83443639941</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Contact 38</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Peat Contractors</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Peat+Contractors</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>46120.83443639942</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Contact 39</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Humus Construction</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Humus+Construction</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>46120.83443639943</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Contact 40</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Loess Renovations</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Loess+Renovations</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>46120.83443639945</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Contact 41</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Regosol Builders</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Regosol+Builders</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>46120.83443639945</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Contact 42</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Chernozem Contractors</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Chernozem+Contractors</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>46120.83443639947</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Contact 43</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Podzol Construction</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Podzol+Construction</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>83216874</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>46120.83443639948</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Contact 44</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Gleysol Renovations</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Gleysol+Renovations</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
+        <v>46120.83443639949</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Contact 45</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Histosol Builders</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Histosol+Builders</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>46120.83443639949</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Contact 46</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Andisol Contractors</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Andisol+Contractors</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>18396882874</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="n">
+        <v>46120.83443639951</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Contact 47</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Oxisol Construction</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Oxisol+Construction</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>46120.83443639951</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Contact 48</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Ultisol Renovations</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Ultisol+Renovations</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>608512996</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="n">
+        <v>46120.83443639955</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Contact 49</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Alfisol Builders</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Alfisol+Builders</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>492396986</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="n">
+        <v>46120.83443639955</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Contact 50</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Mollisol Contractors</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>https://bing.com/search?q=Mollisol+Contractors</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>3732605936979161</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Bing (sample)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="n">
+        <v>46120.83443639956</v>
       </c>
     </row>
   </sheetData>
